--- a/outputs/clinic4/data_distribution.xlsx
+++ b/outputs/clinic4/data_distribution.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3501 (50.5%)</t>
+          <t>3818 (50.6%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.5 ± 9.7</t>
+          <t>55.6 ± 9.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>164.1 ± 8.4</t>
+          <t>164.0 ± 8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23.4 ± 2.8</t>
+          <t>23.4 ± 2.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5168.3 ± 1659.9</t>
+          <t>5167.4 ± 1653.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6374.2 ± 4110.4</t>
+          <t>6377.8 ± 4100.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12437.5 ± 6086.0</t>
+          <t>12437.9 ± 6083.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>746.1 ± 403.0</t>
+          <t>747.9 ± 404.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10776.9 ± 4250.5</t>
+          <t>10768.9 ± 4238.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3294.7 ± 1600.5</t>
+          <t>3298.5 ± 1602.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>14071.6 ± 5156.8</t>
+          <t>14067.4 ± 5140.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1358 (19.6%)</t>
+          <t>1503 (19.9%)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>742 (10.7%)</t>
+          <t>834 (11.1%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
